--- a/grupos/6ASV - Estadisticos 20232.xlsx
+++ b/grupos/6ASV - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="51">
   <si>
     <t>Materia</t>
   </si>
@@ -134,21 +134,21 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
+    <t>Hernández Mendoza Delfina</t>
+  </si>
+  <si>
     <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
     <t>Castillo Cruz Carlos Samuel</t>
   </si>
   <si>
-    <t>Jiménez Nieto Enrique</t>
-  </si>
-  <si>
-    <t>Hernández Mendoza Delfina</t>
-  </si>
-  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
@@ -167,19 +167,10 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
     <t>NAJERA</t>
   </si>
   <si>
-    <t>MIXCOHA</t>
-  </si>
-  <si>
     <t>ALBERTO SHAKIB</t>
-  </si>
-  <si>
-    <t>CRISTHIAN ALFONSO</t>
   </si>
 </sst>
 </file>
@@ -687,22 +678,22 @@
         <v>5</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -723,7 +714,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U4">
         <v>5</v>
@@ -738,7 +729,7 @@
         <v>5</v>
       </c>
       <c r="Y4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -764,19 +755,19 @@
         <v>9</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M5">
         <v>-1</v>
@@ -806,7 +797,7 @@
         <v>8</v>
       </c>
       <c r="V5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W5">
         <v>10</v>
@@ -841,22 +832,22 @@
         <v>8</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -880,19 +871,19 @@
         <v>10</v>
       </c>
       <c r="U6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W6">
         <v>10</v>
       </c>
       <c r="X6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y6">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -918,22 +909,22 @@
         <v>6</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -957,10 +948,10 @@
         <v>10</v>
       </c>
       <c r="U7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W7">
         <v>8</v>
@@ -995,22 +986,22 @@
         <v>5</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1072,22 +1063,22 @@
         <v>10</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1149,22 +1140,22 @@
         <v>5</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1185,22 +1176,22 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W10">
+        <v>5</v>
+      </c>
+      <c r="X10">
+        <v>7</v>
+      </c>
+      <c r="Y10">
         <v>6</v>
-      </c>
-      <c r="X10">
-        <v>6</v>
-      </c>
-      <c r="Y10">
-        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1226,22 +1217,22 @@
         <v>6</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1262,19 +1253,19 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V11">
         <v>10</v>
       </c>
       <c r="W11">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y11">
         <v>6</v>
@@ -1303,22 +1294,22 @@
         <v>8</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1342,7 +1333,7 @@
         <v>10</v>
       </c>
       <c r="U12">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V12">
         <v>10</v>
@@ -1380,22 +1371,22 @@
         <v>5</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1416,13 +1407,13 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U13">
         <v>5</v>
       </c>
       <c r="V13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W13">
         <v>5</v>
@@ -1457,22 +1448,22 @@
         <v>7</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1493,22 +1484,22 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V14">
         <v>10</v>
       </c>
       <c r="W14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X14">
         <v>8</v>
       </c>
       <c r="Y14">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1534,22 +1525,22 @@
         <v>10</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1573,7 +1564,7 @@
         <v>10</v>
       </c>
       <c r="U15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V15">
         <v>10</v>
@@ -1582,10 +1573,10 @@
         <v>9</v>
       </c>
       <c r="X15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y15">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1611,22 +1602,22 @@
         <v>5</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1647,13 +1638,13 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U16">
         <v>5</v>
       </c>
       <c r="V16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W16">
         <v>5</v>
@@ -1688,22 +1679,22 @@
         <v>8</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1724,16 +1715,16 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V17">
         <v>10</v>
       </c>
       <c r="W17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X17">
         <v>10</v>
@@ -1875,40 +1866,40 @@
         <v>41.7</v>
       </c>
       <c r="H4">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="I4">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J4">
         <v>100</v>
       </c>
       <c r="K4">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="L4">
-        <v>81.5</v>
+        <v>77.8</v>
       </c>
       <c r="M4">
-        <v>41.7</v>
+        <v>69.2</v>
       </c>
       <c r="N4">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="O4">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P4">
         <v>100</v>
       </c>
       <c r="Q4">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="R4">
-        <v>81.5</v>
+        <v>77.8</v>
       </c>
       <c r="S4">
-        <v>41.7</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -1949,7 +1940,7 @@
         <v>100</v>
       </c>
       <c r="M5">
-        <v>100</v>
+        <v>92.3</v>
       </c>
       <c r="N5">
         <v>100</v>
@@ -1967,7 +1958,7 @@
         <v>100</v>
       </c>
       <c r="S5">
-        <v>100</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -2005,10 +1996,10 @@
         <v>100</v>
       </c>
       <c r="L6">
-        <v>85.2</v>
+        <v>87</v>
       </c>
       <c r="M6">
-        <v>100</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="N6">
         <v>100</v>
@@ -2023,10 +2014,10 @@
         <v>100</v>
       </c>
       <c r="R6">
-        <v>85.2</v>
+        <v>87</v>
       </c>
       <c r="S6">
-        <v>100</v>
+        <v>90.40000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -2052,7 +2043,7 @@
         <v>91.7</v>
       </c>
       <c r="H7">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="I7">
         <v>100</v>
@@ -2064,13 +2055,13 @@
         <v>100</v>
       </c>
       <c r="L7">
-        <v>96.3</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="M7">
-        <v>91.7</v>
+        <v>96.2</v>
       </c>
       <c r="N7">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="O7">
         <v>100</v>
@@ -2082,10 +2073,10 @@
         <v>100</v>
       </c>
       <c r="R7">
-        <v>96.3</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="S7">
-        <v>91.7</v>
+        <v>96.2</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -2117,7 +2108,7 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -2135,7 +2126,7 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -2229,7 +2220,7 @@
         <v>91.7</v>
       </c>
       <c r="H10">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="I10">
         <v>100</v>
@@ -2244,10 +2235,10 @@
         <v>100</v>
       </c>
       <c r="M10">
-        <v>91.7</v>
+        <v>96.2</v>
       </c>
       <c r="N10">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="O10">
         <v>100</v>
@@ -2262,7 +2253,7 @@
         <v>100</v>
       </c>
       <c r="S10">
-        <v>91.7</v>
+        <v>96.2</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -2300,10 +2291,10 @@
         <v>100</v>
       </c>
       <c r="L11">
-        <v>100</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="M11">
-        <v>95.8</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="N11">
         <v>100</v>
@@ -2318,10 +2309,10 @@
         <v>100</v>
       </c>
       <c r="R11">
-        <v>100</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="S11">
-        <v>95.8</v>
+        <v>98.09999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -2359,7 +2350,7 @@
         <v>100</v>
       </c>
       <c r="L12">
-        <v>96.3</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="M12">
         <v>100</v>
@@ -2377,7 +2368,7 @@
         <v>100</v>
       </c>
       <c r="R12">
-        <v>96.3</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="S12">
         <v>100</v>
@@ -2409,37 +2400,37 @@
         <v>100</v>
       </c>
       <c r="I13">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="J13">
         <v>100</v>
       </c>
       <c r="K13">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="L13">
-        <v>63</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="M13">
-        <v>41.7</v>
+        <v>48.1</v>
       </c>
       <c r="N13">
         <v>100</v>
       </c>
       <c r="O13">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="P13">
         <v>100</v>
       </c>
       <c r="Q13">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="R13">
-        <v>63</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="S13">
-        <v>41.7</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -2477,7 +2468,7 @@
         <v>100</v>
       </c>
       <c r="L14">
-        <v>100</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="M14">
         <v>100</v>
@@ -2495,7 +2486,7 @@
         <v>100</v>
       </c>
       <c r="R14">
-        <v>100</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="S14">
         <v>100</v>
@@ -2536,7 +2527,7 @@
         <v>100</v>
       </c>
       <c r="L15">
-        <v>88.90000000000001</v>
+        <v>87</v>
       </c>
       <c r="M15">
         <v>100</v>
@@ -2554,7 +2545,7 @@
         <v>100</v>
       </c>
       <c r="R15">
-        <v>88.90000000000001</v>
+        <v>87</v>
       </c>
       <c r="S15">
         <v>100</v>
@@ -2586,37 +2577,37 @@
         <v>100</v>
       </c>
       <c r="I16">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="J16">
         <v>100</v>
       </c>
       <c r="K16">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="L16">
-        <v>81.5</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="M16">
-        <v>41.7</v>
+        <v>48.1</v>
       </c>
       <c r="N16">
         <v>100</v>
       </c>
       <c r="O16">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="P16">
         <v>100</v>
       </c>
       <c r="Q16">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="R16">
-        <v>81.5</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="S16">
-        <v>41.7</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -2654,7 +2645,7 @@
         <v>100</v>
       </c>
       <c r="L17">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="M17">
         <v>100</v>
@@ -2672,7 +2663,7 @@
         <v>100</v>
       </c>
       <c r="R17">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="S17">
         <v>100</v>
@@ -2732,7 +2723,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>38</v>
@@ -2741,19 +2732,19 @@
         <v>14</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" s="2">
-        <v>57.1</v>
+        <v>64.3</v>
       </c>
       <c r="G2" s="2">
-        <v>42.9</v>
+        <v>35.7</v>
       </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -2764,7 +2755,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>39</v>
@@ -2773,19 +2764,19 @@
         <v>14</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3" s="2">
-        <v>64.3</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G3" s="2">
-        <v>35.7</v>
+        <v>28.6</v>
       </c>
       <c r="H3">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -2796,7 +2787,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>40</v>
@@ -2817,7 +2808,7 @@
         <v>28.6</v>
       </c>
       <c r="H4">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2828,7 +2819,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>41</v>
@@ -2837,19 +2828,19 @@
         <v>14</v>
       </c>
       <c r="D5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>71.40000000000001</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="G5" s="2">
-        <v>28.6</v>
+        <v>21.4</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -2860,7 +2851,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>42</v>
@@ -2869,19 +2860,19 @@
         <v>14</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2">
-        <v>71.40000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="G6" s="2">
-        <v>28.6</v>
+        <v>14.3</v>
       </c>
       <c r="H6">
-        <v>7.3</v>
+        <v>8.4</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -2913,7 +2904,7 @@
         <v>7.1</v>
       </c>
       <c r="H7">
-        <v>8.1</v>
+        <v>8.6</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -2963,7 +2954,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3001,64 +2992,18 @@
         <v>48</v>
       </c>
       <c r="C2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" t="s">
         <v>50</v>
       </c>
-      <c r="D2" t="s">
-        <v>52</v>
-      </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
         <v>38</v>
       </c>
       <c r="G2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920141</v>
-      </c>
-      <c r="B3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920139</v>
-      </c>
-      <c r="B4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" t="s">
-        <v>38</v>
-      </c>
-      <c r="G4">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6ASV - Estadisticos 20232.xlsx
+++ b/grupos/6ASV - Estadisticos 20232.xlsx
@@ -1863,7 +1863,7 @@
         <v>81.5</v>
       </c>
       <c r="G4">
-        <v>41.7</v>
+        <v>91.7</v>
       </c>
       <c r="H4">
         <v>96.7</v>
@@ -1881,7 +1881,7 @@
         <v>77.8</v>
       </c>
       <c r="M4">
-        <v>69.2</v>
+        <v>92.3</v>
       </c>
       <c r="N4">
         <v>96.7</v>
@@ -1899,7 +1899,7 @@
         <v>77.8</v>
       </c>
       <c r="S4">
-        <v>69.2</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="5" spans="1:19">

--- a/grupos/6ASV - Estadisticos 20232.xlsx
+++ b/grupos/6ASV - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="55">
   <si>
     <t>Materia</t>
   </si>
@@ -77,6 +77,9 @@
     <t>HERNANDEZ NAJERA ALBERTO SHAKIB</t>
   </si>
   <si>
+    <t>MARTINEZ SANTOS ANGEL GABRIEL</t>
+  </si>
+  <si>
     <t>ORTEGA HERNANDEZ ALEXIS ISAI</t>
   </si>
   <si>
@@ -137,21 +140,21 @@
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
+    <t>Duran Amezcua María Angélica</t>
+  </si>
+  <si>
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
     <t>Hernández Mendoza Delfina</t>
   </si>
   <si>
-    <t>Duran Amezcua María Angélica</t>
+    <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
     <t>Castillo Cruz Carlos Samuel</t>
   </si>
   <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -164,13 +167,22 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>ALBERTO SHAKIB</t>
+    <t>PEDRO ANGEL</t>
+  </si>
+  <si>
+    <t>LUIS GUILLERMO</t>
   </si>
 </sst>
 </file>
@@ -532,7 +544,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y17"/>
+  <dimension ref="A1:Y18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -696,31 +708,31 @@
         <v>7</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T4">
         <v>8</v>
       </c>
       <c r="U4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W4">
         <v>5</v>
@@ -729,7 +741,7 @@
         <v>5</v>
       </c>
       <c r="Y4">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -770,28 +782,28 @@
         <v>9</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U5">
         <v>8</v>
@@ -803,7 +815,7 @@
         <v>10</v>
       </c>
       <c r="X5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y5">
         <v>9</v>
@@ -850,22 +862,22 @@
         <v>9</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>10</v>
@@ -927,25 +939,25 @@
         <v>6</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U7">
         <v>7</v>
@@ -954,7 +966,7 @@
         <v>9</v>
       </c>
       <c r="W7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X7">
         <v>8</v>
@@ -1004,22 +1016,22 @@
         <v>5</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T8">
         <v>5</v>
@@ -1081,22 +1093,22 @@
         <v>9</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T9">
         <v>10</v>
@@ -1114,7 +1126,7 @@
         <v>10</v>
       </c>
       <c r="Y9">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1158,34 +1170,34 @@
         <v>7</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T10">
         <v>8</v>
       </c>
       <c r="U10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V10">
         <v>9</v>
       </c>
       <c r="W10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X10">
         <v>7</v>
@@ -1199,10 +1211,10 @@
         <v>19</v>
       </c>
       <c r="B11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C11">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -1211,64 +1223,64 @@
         <v>9</v>
       </c>
       <c r="F11">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J11">
         <v>10</v>
       </c>
       <c r="K11">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U11">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V11">
         <v>10</v>
       </c>
       <c r="W11">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y11">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1276,10 +1288,10 @@
         <v>20</v>
       </c>
       <c r="B12">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D12">
         <v>10</v>
@@ -1288,64 +1300,64 @@
         <v>9</v>
       </c>
       <c r="F12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G12">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J12">
         <v>10</v>
       </c>
       <c r="K12">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L12">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M12">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U12">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V12">
         <v>10</v>
       </c>
       <c r="W12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X12">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y12">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1353,76 +1365,76 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D13">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E13">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F13">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G13">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I13">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K13">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L13">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M13">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U13">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W13">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="X13">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Y13">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1433,73 +1445,73 @@
         <v>7</v>
       </c>
       <c r="C14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D14">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H14">
         <v>8</v>
       </c>
       <c r="I14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T14">
         <v>8</v>
       </c>
       <c r="U14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="X14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y14">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1507,64 +1519,64 @@
         <v>23</v>
       </c>
       <c r="B15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D15">
         <v>10</v>
       </c>
       <c r="E15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J15">
         <v>10</v>
       </c>
       <c r="K15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V15">
         <v>10</v>
@@ -1573,10 +1585,10 @@
         <v>9</v>
       </c>
       <c r="X15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y15">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1584,76 +1596,76 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C16">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D16">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E16">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G16">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I16">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K16">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L16">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M16">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U16">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W16">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="X16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y16">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1664,73 +1676,150 @@
         <v>7</v>
       </c>
       <c r="C17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D17">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E17">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F17">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G17">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H17">
         <v>8</v>
       </c>
       <c r="I17">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K17">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L17">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M17">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T17">
         <v>8</v>
       </c>
       <c r="U17">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V17">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W17">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="X17">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25">
+      <c r="A18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18">
+        <v>7</v>
+      </c>
+      <c r="C18">
+        <v>6</v>
+      </c>
+      <c r="D18">
+        <v>10</v>
+      </c>
+      <c r="E18">
+        <v>8</v>
+      </c>
+      <c r="F18">
+        <v>10</v>
+      </c>
+      <c r="G18">
+        <v>8</v>
+      </c>
+      <c r="H18">
+        <v>8</v>
+      </c>
+      <c r="I18">
+        <v>9</v>
+      </c>
+      <c r="J18">
+        <v>10</v>
+      </c>
+      <c r="K18">
+        <v>9</v>
+      </c>
+      <c r="L18">
+        <v>9</v>
+      </c>
+      <c r="M18">
+        <v>8</v>
+      </c>
+      <c r="N18">
+        <v>8</v>
+      </c>
+      <c r="O18">
+        <v>8</v>
+      </c>
+      <c r="P18">
+        <v>10</v>
+      </c>
+      <c r="Q18">
+        <v>10</v>
+      </c>
+      <c r="R18">
+        <v>8</v>
+      </c>
+      <c r="S18">
+        <v>10</v>
+      </c>
+      <c r="T18">
+        <v>8</v>
+      </c>
+      <c r="U18">
+        <v>8</v>
+      </c>
+      <c r="V18">
+        <v>10</v>
+      </c>
+      <c r="W18">
+        <v>9</v>
+      </c>
+      <c r="X18">
+        <v>9</v>
+      </c>
+      <c r="Y18">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1746,7 +1835,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S17"/>
+  <dimension ref="A1:S18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -1755,7 +1844,7 @@
     <row r="1" spans="1:19">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -1763,7 +1852,7 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -1771,7 +1860,7 @@
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
@@ -1884,22 +1973,22 @@
         <v>92.3</v>
       </c>
       <c r="N4">
-        <v>96.7</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="O4">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="P4">
         <v>100</v>
       </c>
       <c r="Q4">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="R4">
-        <v>77.8</v>
+        <v>77.5</v>
       </c>
       <c r="S4">
-        <v>92.3</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -1958,7 +2047,7 @@
         <v>100</v>
       </c>
       <c r="S5">
-        <v>92.3</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -2014,10 +2103,10 @@
         <v>100</v>
       </c>
       <c r="R6">
-        <v>87</v>
+        <v>91.3</v>
       </c>
       <c r="S6">
-        <v>90.40000000000001</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -2061,7 +2150,7 @@
         <v>96.2</v>
       </c>
       <c r="N7">
-        <v>98.3</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="O7">
         <v>100</v>
@@ -2073,10 +2162,10 @@
         <v>100</v>
       </c>
       <c r="R7">
-        <v>98.09999999999999</v>
+        <v>98.8</v>
       </c>
       <c r="S7">
-        <v>96.2</v>
+        <v>94.8</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -2126,7 +2215,7 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -2238,7 +2327,7 @@
         <v>96.2</v>
       </c>
       <c r="N10">
-        <v>96.7</v>
+        <v>97.8</v>
       </c>
       <c r="O10">
         <v>100</v>
@@ -2250,10 +2339,10 @@
         <v>100</v>
       </c>
       <c r="R10">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="S10">
-        <v>96.2</v>
+        <v>94.8</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -2261,7 +2350,7 @@
         <v>19</v>
       </c>
       <c r="B11">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="C11">
         <v>100</v>
@@ -2276,10 +2365,10 @@
         <v>100</v>
       </c>
       <c r="G11">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="H11">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="I11">
         <v>100</v>
@@ -2291,13 +2380,13 @@
         <v>100</v>
       </c>
       <c r="L11">
-        <v>94.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="M11">
-        <v>98.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="N11">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="O11">
         <v>100</v>
@@ -2309,10 +2398,10 @@
         <v>100</v>
       </c>
       <c r="R11">
-        <v>94.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="S11">
-        <v>98.09999999999999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -2332,10 +2421,10 @@
         <v>100</v>
       </c>
       <c r="F12">
-        <v>96.3</v>
+        <v>100</v>
       </c>
       <c r="G12">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="H12">
         <v>100</v>
@@ -2353,7 +2442,7 @@
         <v>94.40000000000001</v>
       </c>
       <c r="M12">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="N12">
         <v>100</v>
@@ -2368,10 +2457,10 @@
         <v>100</v>
       </c>
       <c r="R12">
-        <v>94.40000000000001</v>
+        <v>95</v>
       </c>
       <c r="S12">
-        <v>100</v>
+        <v>96.09999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -2382,55 +2471,55 @@
         <v>100</v>
       </c>
       <c r="C13">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="D13">
         <v>100</v>
       </c>
       <c r="E13">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="F13">
-        <v>63</v>
+        <v>96.3</v>
       </c>
       <c r="G13">
-        <v>41.7</v>
+        <v>100</v>
       </c>
       <c r="H13">
         <v>100</v>
       </c>
       <c r="I13">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="J13">
         <v>100</v>
       </c>
       <c r="K13">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="L13">
-        <v>70.40000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="M13">
-        <v>48.1</v>
+        <v>100</v>
       </c>
       <c r="N13">
         <v>100</v>
       </c>
       <c r="O13">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="P13">
         <v>100</v>
       </c>
       <c r="Q13">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="R13">
-        <v>70.40000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="S13">
-        <v>48.1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -2441,55 +2530,55 @@
         <v>100</v>
       </c>
       <c r="C14">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="D14">
         <v>100</v>
       </c>
       <c r="E14">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="F14">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="G14">
-        <v>100</v>
+        <v>41.7</v>
       </c>
       <c r="H14">
         <v>100</v>
       </c>
       <c r="I14">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="J14">
         <v>100</v>
       </c>
       <c r="K14">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="L14">
-        <v>94.40000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="M14">
-        <v>100</v>
+        <v>48.1</v>
       </c>
       <c r="N14">
         <v>100</v>
       </c>
       <c r="O14">
-        <v>100</v>
+        <v>78.8</v>
       </c>
       <c r="P14">
         <v>100</v>
       </c>
       <c r="Q14">
-        <v>100</v>
+        <v>81.3</v>
       </c>
       <c r="R14">
-        <v>94.40000000000001</v>
+        <v>80</v>
       </c>
       <c r="S14">
-        <v>100</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -2509,7 +2598,7 @@
         <v>100</v>
       </c>
       <c r="F15">
-        <v>88.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="G15">
         <v>100</v>
@@ -2527,7 +2616,7 @@
         <v>100</v>
       </c>
       <c r="L15">
-        <v>87</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="M15">
         <v>100</v>
@@ -2545,7 +2634,7 @@
         <v>100</v>
       </c>
       <c r="R15">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="S15">
         <v>100</v>
@@ -2559,55 +2648,55 @@
         <v>100</v>
       </c>
       <c r="C16">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="D16">
         <v>100</v>
       </c>
       <c r="E16">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="F16">
-        <v>81.5</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="G16">
-        <v>41.7</v>
+        <v>100</v>
       </c>
       <c r="H16">
         <v>100</v>
       </c>
       <c r="I16">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="J16">
         <v>100</v>
       </c>
       <c r="K16">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="L16">
-        <v>79.59999999999999</v>
+        <v>87</v>
       </c>
       <c r="M16">
-        <v>48.1</v>
+        <v>100</v>
       </c>
       <c r="N16">
         <v>100</v>
       </c>
       <c r="O16">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="P16">
         <v>100</v>
       </c>
       <c r="Q16">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="R16">
-        <v>79.59999999999999</v>
+        <v>86.3</v>
       </c>
       <c r="S16">
-        <v>48.1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -2618,54 +2707,113 @@
         <v>100</v>
       </c>
       <c r="C17">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="D17">
         <v>100</v>
       </c>
       <c r="E17">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="F17">
-        <v>100</v>
+        <v>81.5</v>
       </c>
       <c r="G17">
-        <v>100</v>
+        <v>41.7</v>
       </c>
       <c r="H17">
         <v>100</v>
       </c>
       <c r="I17">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="J17">
         <v>100</v>
       </c>
       <c r="K17">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="L17">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="M17">
+        <v>48.1</v>
+      </c>
+      <c r="N17">
+        <v>100</v>
+      </c>
+      <c r="O17">
+        <v>85</v>
+      </c>
+      <c r="P17">
+        <v>100</v>
+      </c>
+      <c r="Q17">
+        <v>81.3</v>
+      </c>
+      <c r="R17">
+        <v>81.3</v>
+      </c>
+      <c r="S17">
+        <v>45.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
+      <c r="A18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18">
+        <v>100</v>
+      </c>
+      <c r="C18">
+        <v>100</v>
+      </c>
+      <c r="D18">
+        <v>100</v>
+      </c>
+      <c r="E18">
+        <v>100</v>
+      </c>
+      <c r="F18">
+        <v>100</v>
+      </c>
+      <c r="G18">
+        <v>100</v>
+      </c>
+      <c r="H18">
+        <v>100</v>
+      </c>
+      <c r="I18">
+        <v>100</v>
+      </c>
+      <c r="J18">
+        <v>100</v>
+      </c>
+      <c r="K18">
+        <v>100</v>
+      </c>
+      <c r="L18">
         <v>98.09999999999999</v>
       </c>
-      <c r="M17">
-        <v>100</v>
-      </c>
-      <c r="N17">
-        <v>100</v>
-      </c>
-      <c r="O17">
-        <v>100</v>
-      </c>
-      <c r="P17">
-        <v>100</v>
-      </c>
-      <c r="Q17">
-        <v>100</v>
-      </c>
-      <c r="R17">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="S17">
+      <c r="M18">
+        <v>100</v>
+      </c>
+      <c r="N18">
+        <v>100</v>
+      </c>
+      <c r="O18">
+        <v>100</v>
+      </c>
+      <c r="P18">
+        <v>100</v>
+      </c>
+      <c r="Q18">
+        <v>100</v>
+      </c>
+      <c r="R18">
+        <v>98.8</v>
+      </c>
+      <c r="S18">
         <v>100</v>
       </c>
     </row>
@@ -2694,31 +2842,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -2726,25 +2874,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2" s="2">
-        <v>64.3</v>
+        <v>73.3</v>
       </c>
       <c r="G2" s="2">
-        <v>35.7</v>
+        <v>26.7</v>
       </c>
       <c r="H2">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -2755,28 +2903,28 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3" s="2">
-        <v>71.40000000000001</v>
+        <v>80</v>
       </c>
       <c r="G3" s="2">
-        <v>28.6</v>
+        <v>20</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -2787,28 +2935,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2">
-        <v>71.40000000000001</v>
+        <v>86.7</v>
       </c>
       <c r="G4" s="2">
-        <v>28.6</v>
+        <v>13.3</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2819,28 +2967,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2">
-        <v>78.59999999999999</v>
+        <v>86.7</v>
       </c>
       <c r="G5" s="2">
-        <v>21.4</v>
+        <v>13.3</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>7.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -2851,28 +2999,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C6">
+        <v>15</v>
+      </c>
+      <c r="D6">
         <v>14</v>
       </c>
-      <c r="D6">
-        <v>12</v>
-      </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2">
-        <v>85.7</v>
+        <v>93.3</v>
       </c>
       <c r="G6" s="2">
-        <v>14.3</v>
+        <v>6.7</v>
       </c>
       <c r="H6">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -2883,25 +3031,25 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C7">
+        <v>15</v>
+      </c>
+      <c r="D7">
         <v>14</v>
-      </c>
-      <c r="D7">
-        <v>13</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
       <c r="F7" s="2">
-        <v>92.90000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="G7" s="2">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
       <c r="H7">
         <v>8.6</v>
@@ -2929,16 +3077,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -2954,7 +3102,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2963,22 +3111,22 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -2986,24 +3134,93 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920141</v>
+        <v>21330051920135</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>21330051920135</v>
+      </c>
+      <c r="B3" t="s">
         <v>49</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920382</v>
+      </c>
+      <c r="B4" t="s">
         <v>50</v>
       </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G2">
+      <c r="C4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21330051920382</v>
+      </c>
+      <c r="B5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5">
         <v>5</v>
       </c>
     </row>
